--- a/template.xlsx
+++ b/template.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Bad" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gaeste-WC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bad" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,10 +27,13 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -40,17 +42,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00DDE7F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,16 +56,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00999999"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00999999"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00999999"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="00999999"/>
       </bottom>
     </border>
   </borders>
@@ -82,15 +74,11 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,470 +444,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>von</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>bis</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Di</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Mi</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Do</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Fr</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sa</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>So</t>
+          <t>Mo-Fr</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>von</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>17</v>
+          <t>bis</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Temp</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C3" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C5" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C6" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>24:00</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>17</v>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Sa-So</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>von</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>bis</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Temp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>von</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>bis</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Di</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Mi</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Do</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Fr</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sa</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>So</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>24:00</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A9:C9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>